--- a/DATA/Processed/armax_selected_coefficients.xlsx
+++ b/DATA/Processed/armax_selected_coefficients.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F30"/>
+  <dimension ref="A1:F32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -460,16 +460,16 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>-0.0009896659438369713</v>
+        <v>-0.0004584915731436754</v>
       </c>
       <c r="D2" t="n">
-        <v>0.0003537506640673641</v>
+        <v>0.0003471133294773837</v>
       </c>
       <c r="E2" t="n">
-        <v>0.005147793201081173</v>
+        <v>0.1865447242516429</v>
       </c>
       <c r="F2" t="n">
-        <v>-2.797636992275754</v>
+        <v>-1.320869970144862</v>
       </c>
     </row>
     <row r="3">
@@ -484,16 +484,16 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>0.141547957426694</v>
+        <v>0.1435700369385174</v>
       </c>
       <c r="D3" t="n">
-        <v>0.04024618373750379</v>
+        <v>0.03683670683817356</v>
       </c>
       <c r="E3" t="n">
-        <v>0.0004363667980031113</v>
+        <v>9.720201889577785e-05</v>
       </c>
       <c r="F3" t="n">
-        <v>3.517052904938939</v>
+        <v>3.897472094050952</v>
       </c>
     </row>
     <row r="4">
@@ -504,20 +504,20 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>dlog_m2_L3</t>
+          <t>dlog_m2_L5</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>0.08524794789370893</v>
+        <v>0.1079168988982347</v>
       </c>
       <c r="D4" t="n">
-        <v>0.03849801553122169</v>
+        <v>0.04578167466911405</v>
       </c>
       <c r="E4" t="n">
-        <v>0.02680494868728076</v>
+        <v>0.01841296347642932</v>
       </c>
       <c r="F4" t="n">
-        <v>2.214346550527346</v>
+        <v>2.357207325380766</v>
       </c>
     </row>
     <row r="5">
@@ -528,20 +528,20 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>dlog_m2_L5</t>
+          <t>dlog_m2_L6</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>0.09835146530549373</v>
+        <v>-0.06459906887603455</v>
       </c>
       <c r="D5" t="n">
-        <v>0.04200979742382906</v>
+        <v>0.0380530255235371</v>
       </c>
       <c r="E5" t="n">
-        <v>0.01922416204625351</v>
+        <v>0.089582028395639</v>
       </c>
       <c r="F5" t="n">
-        <v>2.341155428893027</v>
+        <v>-1.697606641975887</v>
       </c>
     </row>
     <row r="6">
@@ -556,16 +556,16 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>0.03607929207289966</v>
+        <v>0.03398796247864517</v>
       </c>
       <c r="D6" t="n">
-        <v>0.0159525931073854</v>
+        <v>0.01619989885675797</v>
       </c>
       <c r="E6" t="n">
-        <v>0.02371861034229114</v>
+        <v>0.03590201180207736</v>
       </c>
       <c r="F6" t="n">
-        <v>2.261656887380674</v>
+        <v>2.098035474120674</v>
       </c>
     </row>
     <row r="7">
@@ -576,20 +576,20 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>d_str_L2</t>
+          <t>d_ltr_L1</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>0.008439985156225654</v>
+        <v>0.001878328097339361</v>
       </c>
       <c r="D7" t="n">
-        <v>0.003147900884329895</v>
+        <v>0.001032574206576573</v>
       </c>
       <c r="E7" t="n">
-        <v>0.00733702678252485</v>
+        <v>0.06890025854467198</v>
       </c>
       <c r="F7" t="n">
-        <v>2.681147045715293</v>
+        <v>1.819073230162144</v>
       </c>
     </row>
     <row r="8">
@@ -600,20 +600,20 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>thailand_outlier_1</t>
+          <t>d_str_L2</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>-0.02729059152817335</v>
+        <v>0.006558236200005267</v>
       </c>
       <c r="D8" t="n">
-        <v>0.002637235697424399</v>
+        <v>0.003016327371358629</v>
       </c>
       <c r="E8" t="n">
-        <v>4.265134060366906e-25</v>
+        <v>0.02968670331214538</v>
       </c>
       <c r="F8" t="n">
-        <v>-10.34818069345343</v>
+        <v>2.174245495458696</v>
       </c>
     </row>
     <row r="9">
@@ -624,20 +624,20 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>thailand_outlier_2</t>
+          <t>thailand_outlier_1</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>0.03262571570860022</v>
+        <v>0.0329544355380671</v>
       </c>
       <c r="D9" t="n">
-        <v>0.004728629447144108</v>
+        <v>0.004918703047344611</v>
       </c>
       <c r="E9" t="n">
-        <v>5.214420205927556e-12</v>
+        <v>2.086733777811074e-11</v>
       </c>
       <c r="F9" t="n">
-        <v>6.899613529308111</v>
+        <v>6.699822132148785</v>
       </c>
     </row>
     <row r="10">
@@ -648,20 +648,20 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>ar.L1</t>
+          <t>thailand_outlier_2</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>-0.3451131683849659</v>
+        <v>-0.02663203297476481</v>
       </c>
       <c r="D10" t="n">
-        <v>0.2866177335172303</v>
+        <v>0.002780911259041041</v>
       </c>
       <c r="E10" t="n">
-        <v>0.2285553047714708</v>
+        <v>1.001672436626419e-21</v>
       </c>
       <c r="F10" t="n">
-        <v>-1.204088679893978</v>
+        <v>-9.576728810810202</v>
       </c>
     </row>
     <row r="11">
@@ -672,68 +672,68 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>ma.L1</t>
+          <t>ar.L1</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>0.6550311453556638</v>
+        <v>0.08091412027601752</v>
       </c>
       <c r="D11" t="n">
-        <v>0.2386817371809918</v>
+        <v>0.3375066175628477</v>
       </c>
       <c r="E11" t="n">
-        <v>0.006062704876416415</v>
+        <v>0.8105311716605019</v>
       </c>
       <c r="F11" t="n">
-        <v>2.744370612900958</v>
+        <v>0.2397408408175889</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Philippines</t>
+          <t>Thailand</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>const</t>
+          <t>ar.L2</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>0.00132618044008491</v>
+        <v>-0.2044522236333087</v>
       </c>
       <c r="D12" t="n">
-        <v>0.0002914442887827871</v>
+        <v>0.1328434529706313</v>
       </c>
       <c r="E12" t="n">
-        <v>5.355071128990977e-06</v>
+        <v>0.1237929954951579</v>
       </c>
       <c r="F12" t="n">
-        <v>4.550373745952213</v>
+        <v>-1.53904629141572</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Philippines</t>
+          <t>Thailand</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>dlog_exr_L1</t>
+          <t>ma.L1</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>0.01763175871021666</v>
+        <v>0.2512716135011688</v>
       </c>
       <c r="D13" t="n">
-        <v>0.01047489934011573</v>
+        <v>0.3624317962011808</v>
       </c>
       <c r="E13" t="n">
-        <v>0.09232884080893994</v>
+        <v>0.4881253726940904</v>
       </c>
       <c r="F13" t="n">
-        <v>1.683238963709398</v>
+        <v>0.6932935138000185</v>
       </c>
     </row>
     <row r="14">
@@ -744,20 +744,20 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>dlog_exr_L6</t>
+          <t>const</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>-0.021271188693503</v>
+        <v>0.00132618044008491</v>
       </c>
       <c r="D14" t="n">
-        <v>0.008893029056701102</v>
+        <v>0.0002914442887827871</v>
       </c>
       <c r="E14" t="n">
-        <v>0.01676165246591343</v>
+        <v>5.355071128990977e-06</v>
       </c>
       <c r="F14" t="n">
-        <v>-2.391894657925881</v>
+        <v>4.550373745952213</v>
       </c>
     </row>
     <row r="15">
@@ -768,20 +768,20 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>d_str_L3</t>
+          <t>dlog_exr_L1</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>-0.0009374212784177392</v>
+        <v>0.01763175871021666</v>
       </c>
       <c r="D15" t="n">
-        <v>0.0004090723342759988</v>
+        <v>0.01047489934011573</v>
       </c>
       <c r="E15" t="n">
-        <v>0.02192998968848599</v>
+        <v>0.09232884080893994</v>
       </c>
       <c r="F15" t="n">
-        <v>-2.291578285480598</v>
+        <v>1.683238963709398</v>
       </c>
     </row>
     <row r="16">
@@ -792,20 +792,20 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>d_str_L4</t>
+          <t>dlog_exr_L6</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>0.0007540616352780891</v>
+        <v>-0.021271188693503</v>
       </c>
       <c r="D16" t="n">
-        <v>0.0004119808546180196</v>
+        <v>0.008893029056701102</v>
       </c>
       <c r="E16" t="n">
-        <v>0.06720034768521645</v>
+        <v>0.01676165246591343</v>
       </c>
       <c r="F16" t="n">
-        <v>1.830331741937959</v>
+        <v>-2.391894657925881</v>
       </c>
     </row>
     <row r="17">
@@ -816,20 +816,20 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>ar.L1</t>
+          <t>d_str_L3</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>0.3803706103964061</v>
+        <v>-0.0009374212784177392</v>
       </c>
       <c r="D17" t="n">
-        <v>0.2984114357110121</v>
+        <v>0.0004090723342759988</v>
       </c>
       <c r="E17" t="n">
-        <v>0.2024325893007811</v>
+        <v>0.02192998968848599</v>
       </c>
       <c r="F17" t="n">
-        <v>1.274651587966505</v>
+        <v>-2.291578285480598</v>
       </c>
     </row>
     <row r="18">
@@ -840,68 +840,68 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>ma.L1</t>
+          <t>d_str_L4</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>-0.005886756200815823</v>
+        <v>0.0007540616352780891</v>
       </c>
       <c r="D18" t="n">
-        <v>0.3092961934746005</v>
+        <v>0.0004119808546180196</v>
       </c>
       <c r="E18" t="n">
-        <v>0.9848149818024836</v>
+        <v>0.06720034768521645</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.01903274700760016</v>
+        <v>1.830331741937959</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Korea</t>
+          <t>Philippines</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>const</t>
+          <t>ar.L1</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>0.000716444248768332</v>
+        <v>0.3803706103964061</v>
       </c>
       <c r="D19" t="n">
-        <v>0.0001223002082178233</v>
+        <v>0.2984114357110121</v>
       </c>
       <c r="E19" t="n">
-        <v>4.682526609349754e-09</v>
+        <v>0.2024325893007811</v>
       </c>
       <c r="F19" t="n">
-        <v>5.858078732722238</v>
+        <v>1.274651587966505</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Korea</t>
+          <t>Philippines</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>dlog_exr_L5</t>
+          <t>ma.L1</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>-0.01345299830256276</v>
+        <v>-0.005886756200815823</v>
       </c>
       <c r="D20" t="n">
-        <v>0.007545225470923958</v>
+        <v>0.3092961934746005</v>
       </c>
       <c r="E20" t="n">
-        <v>0.07458929599565954</v>
+        <v>0.9848149818024836</v>
       </c>
       <c r="F20" t="n">
-        <v>-1.782981615911255</v>
+        <v>-0.01903274700760016</v>
       </c>
     </row>
     <row r="21">
@@ -912,20 +912,20 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>d_ltr_L1</t>
+          <t>const</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>0.002016359263718224</v>
+        <v>0.000716444248768332</v>
       </c>
       <c r="D21" t="n">
-        <v>0.0005981807751705555</v>
+        <v>0.0001223002082178233</v>
       </c>
       <c r="E21" t="n">
-        <v>0.0007494501650210647</v>
+        <v>4.682526609349754e-09</v>
       </c>
       <c r="F21" t="n">
-        <v>3.370819236280726</v>
+        <v>5.858078732722238</v>
       </c>
     </row>
     <row r="22">
@@ -936,20 +936,20 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>d_ltr_L2</t>
+          <t>dlog_exr_L5</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>0.001535820211516727</v>
+        <v>-0.01345299830256276</v>
       </c>
       <c r="D22" t="n">
-        <v>0.0005731908466145033</v>
+        <v>0.007545225470923958</v>
       </c>
       <c r="E22" t="n">
-        <v>0.007374936525168557</v>
+        <v>0.07458929599565954</v>
       </c>
       <c r="F22" t="n">
-        <v>2.679422081821266</v>
+        <v>-1.782981615911255</v>
       </c>
     </row>
     <row r="23">
@@ -960,20 +960,20 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>d_str_L3</t>
+          <t>d_ltr_L1</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>0.002559968537604299</v>
+        <v>0.002016359263718224</v>
       </c>
       <c r="D23" t="n">
-        <v>0.0008732585435678925</v>
+        <v>0.0005981807751705555</v>
       </c>
       <c r="E23" t="n">
-        <v>0.003373155406009877</v>
+        <v>0.0007494501650210647</v>
       </c>
       <c r="F23" t="n">
-        <v>2.931512730634134</v>
+        <v>3.370819236280726</v>
       </c>
     </row>
     <row r="24">
@@ -984,68 +984,68 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>ar.L1</t>
+          <t>d_ltr_L2</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>0.08021288089906947</v>
+        <v>0.001535820211516727</v>
       </c>
       <c r="D24" t="n">
-        <v>0.1043379983890225</v>
+        <v>0.0005731908466145033</v>
       </c>
       <c r="E24" t="n">
-        <v>0.4420244102930345</v>
+        <v>0.007374936525168557</v>
       </c>
       <c r="F24" t="n">
-        <v>0.7687791805244059</v>
+        <v>2.679422081821266</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Indonesia</t>
+          <t>Korea</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>const</t>
+          <t>d_str_L3</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>0.0009057217898672527</v>
+        <v>0.002559968537604299</v>
       </c>
       <c r="D25" t="n">
-        <v>0.0001425764499026059</v>
+        <v>0.0008732585435678925</v>
       </c>
       <c r="E25" t="n">
-        <v>2.117961652274144e-10</v>
+        <v>0.003373155406009877</v>
       </c>
       <c r="F25" t="n">
-        <v>6.352534310441535</v>
+        <v>2.931512730634134</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Indonesia</t>
+          <t>Korea</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>dlog_m2_L1</t>
+          <t>ar.L1</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>0.01939433202927517</v>
+        <v>0.08021288089906947</v>
       </c>
       <c r="D26" t="n">
-        <v>0.008001629127369191</v>
+        <v>0.1043379983890225</v>
       </c>
       <c r="E26" t="n">
-        <v>0.01535914951917585</v>
+        <v>0.4420244102930345</v>
       </c>
       <c r="F26" t="n">
-        <v>2.423797919218447</v>
+        <v>0.7687791805244059</v>
       </c>
     </row>
     <row r="27">
@@ -1056,20 +1056,20 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>d_ltr_L4</t>
+          <t>const</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>0.0007371518635663373</v>
+        <v>0.0009057217898672527</v>
       </c>
       <c r="D27" t="n">
-        <v>0.0004374047650165798</v>
+        <v>0.0001425764499026059</v>
       </c>
       <c r="E27" t="n">
-        <v>0.09193352155182588</v>
+        <v>2.117961652274144e-10</v>
       </c>
       <c r="F27" t="n">
-        <v>1.685285398156089</v>
+        <v>6.352534310441535</v>
       </c>
     </row>
     <row r="28">
@@ -1080,20 +1080,20 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>ar.L1</t>
+          <t>dlog_m2_L1</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>-0.617786125774979</v>
+        <v>0.01939433202927517</v>
       </c>
       <c r="D28" t="n">
-        <v>0.1316225417010942</v>
+        <v>0.008001629127369191</v>
       </c>
       <c r="E28" t="n">
-        <v>2.68413102327547e-06</v>
+        <v>0.01535914951917585</v>
       </c>
       <c r="F28" t="n">
-        <v>-4.693619480300945</v>
+        <v>2.423797919218447</v>
       </c>
     </row>
     <row r="29">
@@ -1104,20 +1104,20 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>ar.L2</t>
+          <t>d_ltr_L4</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>-0.2316017081278829</v>
+        <v>0.0007371518635663373</v>
       </c>
       <c r="D29" t="n">
-        <v>0.098135455592464</v>
+        <v>0.0004374047650165798</v>
       </c>
       <c r="E29" t="n">
-        <v>0.01827391458564387</v>
+        <v>0.09193352155182588</v>
       </c>
       <c r="F29" t="n">
-        <v>-2.360020715547256</v>
+        <v>1.685285398156089</v>
       </c>
     </row>
     <row r="30">
@@ -1128,19 +1128,67 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
+          <t>ar.L1</t>
+        </is>
+      </c>
+      <c r="C30" t="n">
+        <v>-0.617786125774979</v>
+      </c>
+      <c r="D30" t="n">
+        <v>0.1316225417010942</v>
+      </c>
+      <c r="E30" t="n">
+        <v>2.68413102327547e-06</v>
+      </c>
+      <c r="F30" t="n">
+        <v>-4.693619480300945</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Indonesia</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>ar.L2</t>
+        </is>
+      </c>
+      <c r="C31" t="n">
+        <v>-0.2316017081278829</v>
+      </c>
+      <c r="D31" t="n">
+        <v>0.098135455592464</v>
+      </c>
+      <c r="E31" t="n">
+        <v>0.01827391458564387</v>
+      </c>
+      <c r="F31" t="n">
+        <v>-2.360020715547256</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Indonesia</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
           <t>ma.L1</t>
         </is>
       </c>
-      <c r="C30" t="n">
+      <c r="C32" t="n">
         <v>0.6933343163582275</v>
       </c>
-      <c r="D30" t="n">
+      <c r="D32" t="n">
         <v>0.1188293447476515</v>
       </c>
-      <c r="E30" t="n">
+      <c r="E32" t="n">
         <v>5.388542654539292e-09</v>
       </c>
-      <c r="F30" t="n">
+      <c r="F32" t="n">
         <v>5.834706215292247</v>
       </c>
     </row>

--- a/DATA/Processed/armax_selected_coefficients.xlsx
+++ b/DATA/Processed/armax_selected_coefficients.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jonas\Documents\GitHub\Masterthesis\DATA\Processed\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2AE8C3D5-289B-4BAB-A206-A293A5C3DA3F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{245BF481-DB6D-4415-81D5-432F5355D4E4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
